--- a/AAII_Financials/Quarterly/AESI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AESI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>AESI</t>
   </si>
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>293200</v>
+      </c>
+      <c r="E8" s="3">
         <v>265600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>249400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>259600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>288700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>297600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>271300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>304400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>287500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>192700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>141100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>157600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>161800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>153400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>149900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>141700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>131300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>59900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>52800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>43300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>44400</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>221300</v>
+      </c>
+      <c r="E9" s="3">
         <v>214000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>187300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>195200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>195900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>206100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>191000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>225300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>202100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>106700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>66600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>67800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>63500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>62600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>75100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>67300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>53500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>30600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>31600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>25700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E10" s="3">
         <v>51600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>62100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>64400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>92800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>91500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>80400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>79100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>85400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>85900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>74600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>89800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>98300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>90900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>74800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>74400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>77800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>29300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>21200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>17600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,123 +1121,129 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-3200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-5300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>700</v>
       </c>
-      <c r="G14" s="3">
-        <v>300</v>
-      </c>
       <c r="H14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I14" s="3">
         <v>7300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>9100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>10200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E15" s="3">
         <v>51600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>48300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>46500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>47100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>41800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>34200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>29800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>28800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>18200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>10200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>9800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8800</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>313100</v>
+      </c>
+      <c r="E17" s="3">
         <v>301200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>269600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>277500</v>
       </c>
-      <c r="G17" s="3">
-        <v>281200</v>
-      </c>
       <c r="H17" s="3">
+        <v>279500</v>
+      </c>
+      <c r="I17" s="3">
         <v>274900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>231500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>280600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>258200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>142800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>91400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>92300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>84000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>79600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>83000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>73000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>58800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>35900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>36700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>29500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>30700</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-35700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-17900</v>
       </c>
-      <c r="G18" s="3">
-        <v>7500</v>
-      </c>
       <c r="H18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="I18" s="3">
         <v>22600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>39900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>23800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>29300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>49900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>49700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>65300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>77800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>73800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>66900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>68700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>72500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>24000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>16100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,138 +1444,145 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>-100</v>
       </c>
       <c r="P20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-21200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E21" s="3">
         <v>16400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>28200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>28600</v>
       </c>
-      <c r="G21" s="3">
-        <v>55000</v>
-      </c>
       <c r="H21" s="3">
+        <v>56600</v>
+      </c>
+      <c r="I21" s="3">
         <v>64700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>74200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>53900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>58300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>68100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>61400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>75700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>87700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>82800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>71100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>73000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>75900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>27600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1550,43 +1590,43 @@
         <v>14800</v>
       </c>
       <c r="E22" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F22" s="3">
         <v>20400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>3800</v>
       </c>
       <c r="P22" s="3">
         <v>3800</v>
       </c>
       <c r="Q22" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1606,138 +1646,147 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-47800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-30900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-33600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>34700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>47100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>64000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>76300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>70600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>63000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>65700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>69100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>21100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-8700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-9800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
-      </c>
-      <c r="R24" s="3">
-        <v>600</v>
       </c>
       <c r="S24" s="3">
         <v>600</v>
       </c>
       <c r="T24" s="3">
+        <v>600</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>500</v>
-      </c>
-      <c r="V24" s="3">
-        <v>100</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-47300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-22200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>26800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>36100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>56300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>71200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>62900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>62600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>65100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>68500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>20800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-47300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-22200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>26800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>35700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>29400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>38500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>62600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>65100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>68500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>20800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>100</v>
       </c>
       <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>21200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-47300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-22200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>26800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>35700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>29400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>38500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>56300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>62600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>65100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>68500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>20800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-47300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-22200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>26800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>35700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>29400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>38500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>56300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>62600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>65100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>68500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>20800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>168200</v>
+      </c>
+      <c r="E41" s="3">
         <v>39800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>40600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>41300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>78800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>68700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>71700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>78600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>104700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>187100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>210200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>264500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>341700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>352700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>82000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>90700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>69000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>53800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>40400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>27300</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,268 +2791,283 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>217500</v>
+      </c>
+      <c r="E43" s="3">
         <v>208400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>180800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>184600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>186000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>244700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>166000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>179900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>197100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>185800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>71200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>102200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>85900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>95100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>74400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>72600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>74000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>33100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>29400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19900</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E44" s="3">
         <v>66100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>61700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>56800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>55600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>51200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>40600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>37900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>41500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>34900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>21900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>18900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>16800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>16000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3100</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>16700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>479100</v>
+      </c>
+      <c r="E46" s="3">
         <v>335900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>307500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>297200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>334500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>376400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>289400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>316500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>365200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>425500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>318700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>401500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>454300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>470700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>178700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>179900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>157500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>99800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>84300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>59600</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3005,8 +3110,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3026,123 +3131,129 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1625400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1632400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1584600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1587200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1574500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1574000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1504900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1469200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1426100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1308900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>938800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>833500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>740800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>631100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>564700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>520700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>477900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>468500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>458300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>454400</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>322500</v>
+      </c>
+      <c r="E49" s="3">
         <v>329200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>335100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>345900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>335500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>340000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>174900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>184500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>187600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>203600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1800</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,73 +3403,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>128400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1700</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2555300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2298600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2228400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2233500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2247800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2294800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1972700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1973500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1982300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1941700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1261700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1239300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1198600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1103900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>751000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>706800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>639800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>571600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>543900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>515700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,398 +3661,417 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E57" s="3">
         <v>101000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>69200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>92800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>90600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>115500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>119200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>124800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>103800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>102100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>60900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>57500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>47700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>34300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>31800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>29300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8300</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E58" s="3">
         <v>78100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>47500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>43400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>42100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>41000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>53200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>45100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>40300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>34500</v>
-      </c>
-      <c r="M58" s="3">
-        <v>1400</v>
       </c>
       <c r="N58" s="3">
         <v>1400</v>
       </c>
       <c r="O58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P58" s="3">
         <v>37800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>30800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>23800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>18800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>17500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>16700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>15600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>30700</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E59" s="3">
         <v>11400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>33100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>41200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>32900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8300</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>262700</v>
+      </c>
+      <c r="E60" s="3">
         <v>286100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>211100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>220600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>214700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>232000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>243100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>258200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>239300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>190100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>92600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>100600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>141200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>104200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>88700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>89400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>70500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>45900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>40600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>47200</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>981700</v>
+      </c>
+      <c r="E61" s="3">
         <v>614500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>574300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>540200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>510400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>508100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>476900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>450600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>461200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>469200</v>
-      </c>
-      <c r="M61" s="3">
-        <v>176600</v>
       </c>
       <c r="N61" s="3">
         <v>176600</v>
       </c>
       <c r="O61" s="3">
+        <v>176600</v>
+      </c>
+      <c r="P61" s="3">
         <v>137800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>140500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>143500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>146600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>148600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>158400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>159700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>122600</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E62" s="3">
         <v>12600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1442300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1129700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1019500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1010100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>976400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>993700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>936100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>927300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>920400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>875300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>393900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>328100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>319500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>269400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>239600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>243100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>226400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>211900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>205200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>174100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-122700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-97600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-50300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4300</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-14500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-41300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-77000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>31500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>84700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>37100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-12900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-66400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-87300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-71600</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1113000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1168900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1208900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1223400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1271300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1301100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1036600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1046200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1062000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1066400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>867800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-76000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>76700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>56500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>511400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>463600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>413400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>359700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>338700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>341600</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-47300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-22200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>26800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>35700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>29400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>38500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>56300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>62600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>65100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>68500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>20800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,73 +5214,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E83" s="3">
         <v>38800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>33800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>26600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>18100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6700</v>
-      </c>
-      <c r="T83" s="3">
-        <v>6500</v>
       </c>
       <c r="U83" s="3">
         <v>6500</v>
       </c>
       <c r="V83" s="3">
-        <v>6200</v>
+        <v>6500</v>
       </c>
       <c r="W83" s="3">
         <v>6200</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>19000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>32400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>88600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>70900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>85200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>60900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>39600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>85500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>55400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>103900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>54200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>50000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>80600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>51700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>23700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>14100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-153800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-29300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-21800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-33800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-40300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-52400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-76400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-86300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-115800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-95500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-119800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-98900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-85900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-60900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-35400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-35700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-151500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-56500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-40300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-228500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-82900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-76300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-115800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-237700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-119800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-98900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-85900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-60900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-35400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-35700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,52 +6014,53 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F96" s="3">
-        <v>30900</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
         <v>30900</v>
       </c>
       <c r="H96" s="3">
+        <v>30900</v>
+      </c>
+      <c r="I96" s="3">
         <v>30400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>26500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>25300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>24200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>21000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>20000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>27200</v>
-      </c>
-      <c r="O96" s="3">
-        <v>15000</v>
       </c>
       <c r="P96" s="3">
         <v>15000</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>280500</v>
+      </c>
+      <c r="E100" s="3">
         <v>2800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>15200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-38200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>232900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-35000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-27500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>175100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-20100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-33700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-29000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>277400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-23300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-23100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-24200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>30100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6150,8 +6399,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6171,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>128400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-37500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-26100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-82400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-23100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-54400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-77100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>270600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>21700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>15200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>13100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4300</v>
       </c>
     </row>
